--- a/design/蛋仔--大富翁--地图示例.xlsx
+++ b/design/蛋仔--大富翁--地图示例.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lzx_8\Documents\lzx\eggitor\1_开发中\大富翁\设计文档\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\eggitor\1_开发中\大富翁\monopoly\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E48BCAA5-E92B-4F97-BE0F-CEEC5F316EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B22C39F5-1A73-476A-BCDA-86933EB77B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="地图示例" sheetId="1" r:id="rId1"/>
@@ -473,17 +473,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -511,6 +511,13 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -682,7 +689,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -727,6 +734,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1008,20 +1021,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.375" customWidth="1"/>
+    <col min="4" max="4" width="13.625" customWidth="1"/>
+    <col min="5" max="5" width="14.25" customWidth="1"/>
+    <col min="6" max="6" width="10.625" customWidth="1"/>
+    <col min="7" max="7" width="11.875" customWidth="1"/>
+    <col min="8" max="8" width="10.625" customWidth="1"/>
+    <col min="9" max="9" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="38.25" customHeight="1">
+    <row r="1" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C1">
         <v>700</v>
       </c>
@@ -1041,7 +1054,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="37.5" customHeight="1">
+    <row r="2" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="7" t="s">
         <v>57</v>
       </c>
@@ -1073,7 +1086,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="37.5" customHeight="1">
+    <row r="3" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>650</v>
       </c>
@@ -1103,7 +1116,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="37.5" customHeight="1">
+    <row r="4" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>600</v>
       </c>
@@ -1133,7 +1146,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="37.5" customHeight="1">
+    <row r="5" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>550</v>
       </c>
@@ -1174,7 +1187,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="37.5" customHeight="1">
+    <row r="6" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>27</v>
       </c>
@@ -1209,7 +1222,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="37.5" customHeight="1">
+    <row r="7" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>500</v>
       </c>
@@ -1237,7 +1250,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="37.5" customHeight="1">
+    <row r="8" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>450</v>
       </c>
@@ -1267,7 +1280,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="37.5" customHeight="1">
+    <row r="9" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>400</v>
       </c>
@@ -1308,7 +1321,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="37.5" customHeight="1">
+    <row r="10" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
         <v>39</v>
       </c>
@@ -1343,13 +1356,13 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="37.5" customHeight="1">
+    <row r="11" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J11" s="1"/>
       <c r="M11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="37.5" customHeight="1">
+    <row r="12" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>0</v>
       </c>
@@ -1384,7 +1397,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="37.5" customHeight="1">
+    <row r="13" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>1</v>
       </c>
@@ -1400,8 +1413,8 @@
       <c r="E13" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>118</v>
+      <c r="F13" s="28" t="s">
+        <v>115</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>92</v>
@@ -1409,7 +1422,7 @@
       <c r="H13" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="29" t="s">
         <v>94</v>
       </c>
       <c r="J13" s="7" t="s">
@@ -1419,7 +1432,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="37.5" customHeight="1">
+    <row r="14" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1428,20 +1441,20 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="29" t="s">
         <v>106</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="29" t="s">
         <v>95</v>
       </c>
       <c r="M14" s="9" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="37.5" customHeight="1">
+    <row r="15" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>3</v>
       </c>
@@ -1463,7 +1476,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="37.5" customHeight="1">
+    <row r="16" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>4</v>
       </c>
@@ -1476,7 +1489,6 @@
       <c r="F16" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="3" t="s">
@@ -1486,7 +1498,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="37.5" customHeight="1">
+    <row r="17" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>5</v>
       </c>
@@ -1505,8 +1517,8 @@
       <c r="F17" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>115</v>
+      <c r="G17" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>109</v>
@@ -1521,7 +1533,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="37.5" customHeight="1">
+    <row r="18" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>6</v>
       </c>
@@ -1540,11 +1552,11 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="37.5" customHeight="1">
+    <row r="19" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>7</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="29" t="s">
         <v>84</v>
       </c>
       <c r="C19" s="2"/>
@@ -1555,28 +1567,28 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
-      <c r="J19" s="3" t="s">
+      <c r="J19" s="29" t="s">
         <v>99</v>
       </c>
       <c r="M19" s="9" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="37.5" customHeight="1">
+    <row r="20" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>8</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>116</v>
+      <c r="F20" s="6" t="s">
+        <v>119</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="35.25" customHeight="1">
+    <row r="21" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>9</v>
       </c>
@@ -1592,8 +1604,8 @@
       <c r="E21" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F21" s="6" t="s">
-        <v>119</v>
+      <c r="F21" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>69</v>
@@ -1608,46 +1620,46 @@
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="15.75">
+    <row r="23" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="J23" s="1"/>
     </row>
-    <row r="24" spans="1:13" ht="15.75">
+    <row r="24" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="J24" s="1"/>
     </row>
-    <row r="25" spans="1:13" ht="15.75">
+    <row r="25" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="J25" s="1"/>
     </row>
-    <row r="26" spans="1:13" ht="15.75">
+    <row r="26" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="J26" s="1"/>
     </row>
-    <row r="27" spans="1:13" ht="15.75">
+    <row r="27" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="J27" s="1"/>
     </row>
-    <row r="28" spans="1:13" ht="15.75">
+    <row r="28" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="J28" s="1"/>
     </row>
-    <row r="29" spans="1:13" ht="15.75">
+    <row r="29" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="J29" s="1"/>
     </row>
-    <row r="30" spans="1:13" ht="15.75">
+    <row r="30" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="J30" s="1"/>
     </row>
-    <row r="31" spans="1:13" ht="15.75">
+    <row r="31" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="J31" s="1"/>
     </row>
-    <row r="32" spans="1:13" ht="15.75">
+    <row r="32" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="J32" s="1"/>
     </row>
-    <row r="33" spans="10:10" ht="15.75">
+    <row r="33" spans="10:10" ht="15" x14ac:dyDescent="0.2">
       <c r="J33" s="1"/>
     </row>
-    <row r="34" spans="10:10" ht="15.75">
+    <row r="34" spans="10:10" ht="15" x14ac:dyDescent="0.2">
       <c r="J34" s="1"/>
     </row>
-    <row r="35" spans="10:10" ht="15.75">
+    <row r="35" spans="10:10" ht="15" x14ac:dyDescent="0.2">
       <c r="J35" s="1"/>
     </row>
-    <row r="36" spans="10:10" ht="15.75">
+    <row r="36" spans="10:10" ht="15" x14ac:dyDescent="0.2">
       <c r="J36" s="1"/>
     </row>
   </sheetData>
@@ -1660,14 +1672,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BE14419-70B3-4901-BF65-072011132B26}">
   <dimension ref="D4:O19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="4" spans="4:15">
+    <row r="4" spans="4:15" x14ac:dyDescent="0.2">
       <c r="M4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="4:15">
+    <row r="5" spans="4:15" x14ac:dyDescent="0.2">
       <c r="N5" s="11" t="s">
         <v>48</v>
       </c>
@@ -1675,7 +1687,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="4:15">
+    <row r="6" spans="4:15" x14ac:dyDescent="0.2">
       <c r="D6" s="14"/>
       <c r="E6" s="15"/>
       <c r="F6" s="15"/>
@@ -1692,7 +1704,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="4:15">
+    <row r="7" spans="4:15" x14ac:dyDescent="0.2">
       <c r="D7" s="17"/>
       <c r="J7" s="18"/>
       <c r="N7" s="13" t="s">
@@ -1702,49 +1714,49 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="4:15">
+    <row r="8" spans="4:15" x14ac:dyDescent="0.2">
       <c r="D8" s="19" t="s">
         <v>44</v>
       </c>
       <c r="J8" s="18"/>
     </row>
-    <row r="9" spans="4:15">
+    <row r="9" spans="4:15" x14ac:dyDescent="0.2">
       <c r="D9" s="19"/>
       <c r="J9" s="18"/>
     </row>
-    <row r="10" spans="4:15">
+    <row r="10" spans="4:15" x14ac:dyDescent="0.2">
       <c r="D10" s="20" t="s">
         <v>45</v>
       </c>
       <c r="J10" s="18"/>
     </row>
-    <row r="11" spans="4:15">
+    <row r="11" spans="4:15" x14ac:dyDescent="0.2">
       <c r="D11" s="20"/>
       <c r="J11" s="18"/>
     </row>
-    <row r="12" spans="4:15">
+    <row r="12" spans="4:15" x14ac:dyDescent="0.2">
       <c r="D12" s="19" t="s">
         <v>46</v>
       </c>
       <c r="J12" s="18"/>
     </row>
-    <row r="13" spans="4:15">
+    <row r="13" spans="4:15" x14ac:dyDescent="0.2">
       <c r="D13" s="19"/>
       <c r="J13" s="21" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="4:15">
+    <row r="14" spans="4:15" x14ac:dyDescent="0.2">
       <c r="D14" s="20" t="s">
         <v>47</v>
       </c>
       <c r="J14" s="18"/>
     </row>
-    <row r="15" spans="4:15">
+    <row r="15" spans="4:15" x14ac:dyDescent="0.2">
       <c r="D15" s="20"/>
       <c r="J15" s="21"/>
     </row>
-    <row r="16" spans="4:15">
+    <row r="16" spans="4:15" x14ac:dyDescent="0.2">
       <c r="D16" s="17"/>
       <c r="I16" s="22" t="s">
         <v>56</v>
@@ -1753,11 +1765,11 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="4:10">
+    <row r="17" spans="4:10" x14ac:dyDescent="0.2">
       <c r="D17" s="17"/>
       <c r="J17" s="21"/>
     </row>
-    <row r="18" spans="4:10">
+    <row r="18" spans="4:10" x14ac:dyDescent="0.2">
       <c r="D18" s="17"/>
       <c r="E18" s="23"/>
       <c r="F18" s="23"/>
@@ -1768,7 +1780,7 @@
       <c r="I18" s="23"/>
       <c r="J18" s="18"/>
     </row>
-    <row r="19" spans="4:10">
+    <row r="19" spans="4:10" x14ac:dyDescent="0.2">
       <c r="D19" s="24"/>
       <c r="E19" s="26"/>
       <c r="F19" s="26"/>
